--- a/Supplemental_data/Supplemental data 13.xlsx
+++ b/Supplemental_data/Supplemental data 13.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="135">
   <si>
-    <t>Differentially expressed differentially methylated genes (DEDMGs ) shared by all three ecotypes</t>
+    <t>Differentially expressed differentially methylated genes shared by all ecotypes</t>
   </si>
   <si>
     <t xml:space="preserve">In column G, letter G, L and NA represent methylation gain, loss and not available, respectively. </t>
@@ -429,7 +429,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -448,12 +448,17 @@
     <font>
       <sz val="12.0"/>
       <color rgb="FF000000"/>
-      <name val="'Times New Roman'"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color rgb="FF222222"/>
-      <name val="&quot;Google Sans&quot;"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="'Times New Roman'"/>
     </font>
     <font>
       <b/>
@@ -600,43 +605,43 @@
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -645,63 +650,63 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
